--- a/public/exports-from-60-with-coowners/70960516.xlsx
+++ b/public/exports-from-60-with-coowners/70960516.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports-from-60-with-coowners/70960516.xlsx
+++ b/public/exports-from-60-with-coowners/70960516.xlsx
@@ -2141,26 +2141,26 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 8</t>
+          <t xml:space="preserve">Stampevej 10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381978</t>
+          <t xml:space="preserve">2370057</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J29">
-        <v>2800</v>
+        <v>82</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 8</t>
+          <t xml:space="preserve">Ulvemosen 5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2226,16 +2226,16 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381978</t>
+          <t xml:space="preserve">1310679</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J30">
-        <v>200</v>
+        <v>304</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2291,17 +2291,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stampevej 10</t>
+          <t xml:space="preserve">Ulvemosen 7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2370057</t>
+          <t xml:space="preserve">2366592</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="J31">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2366,26 +2366,26 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulvemosen 5</t>
+          <t xml:space="preserve">Ådalsparkvej 2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310679</t>
+          <t xml:space="preserve">2369282</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J32">
-        <v>304</v>
+        <v>600</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2441,26 +2441,26 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulvemosen 7</t>
+          <t xml:space="preserve">Ådalsparkvej 2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366592</t>
+          <t xml:space="preserve">2369282</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J33">
-        <v>205</v>
+        <v>454</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 2</t>
+          <t xml:space="preserve">Ådalsparkvej 4A</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2531,11 +2531,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J34">
-        <v>600</v>
+        <v>196</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 2</t>
+          <t xml:space="preserve">Ådalsparkvej 4E</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2606,11 +2606,11 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J35">
-        <v>454</v>
+        <v>294</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2666,45 +2666,45 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 4A</t>
+          <t xml:space="preserve">Rungsted Havn 8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369282</t>
+          <t xml:space="preserve">2381217, 100749912</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J36">
-        <v>196</v>
+        <v>363</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">100144275</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BygTechA/S</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-12-10</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2741,45 +2741,45 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 4E</t>
+          <t xml:space="preserve">Stadionalle 7A</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369282</t>
+          <t xml:space="preserve">717973, 2370957</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J37">
-        <v>294</v>
+        <v>3096</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200052253</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">LuVa Consult APS</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-08-23</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungsted Havn 8</t>
+          <t xml:space="preserve">Stadionalle 9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2826,30 +2826,30 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381217, 100749912</t>
+          <t xml:space="preserve">717970, 2370954</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J38">
-        <v>363</v>
+        <v>4496</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">100144275</t>
+          <t xml:space="preserve">200056359</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t xml:space="preserve">BygTechA/S</t>
+          <t xml:space="preserve">LuVa Consult APS</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-10</t>
+          <t xml:space="preserve">2021-12-30</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 7A</t>
+          <t xml:space="preserve">Rungsted Havn 32</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">717973, 2370957</t>
+          <t xml:space="preserve">717952, 2381218</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2910,21 +2910,21 @@
         </is>
       </c>
       <c r="J39">
-        <v>3096</v>
+        <v>476</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052253</t>
+          <t xml:space="preserve">311065041</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuVa Consult APS</t>
+          <t xml:space="preserve">CONSU bygningsrådgivning ApS</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-23</t>
+          <t xml:space="preserve">2024-07-16</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 9</t>
+          <t xml:space="preserve">Rungsted Havn 34</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2976,40 +2976,40 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">717970, 2370954</t>
+          <t xml:space="preserve">717938, 7644227</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J40">
-        <v>4496</v>
+        <v>303</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056359</t>
+          <t xml:space="preserve">311217548</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuVa Consult APS</t>
+          <t xml:space="preserve">BF Byggeservice ApS</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-30</t>
+          <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3041,50 +3041,50 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungsted Havn 32</t>
+          <t xml:space="preserve">Alsvej 83</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">717952, 2381218</t>
+          <t xml:space="preserve">2368570</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J41">
-        <v>476</v>
+        <v>341</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311065041</t>
+          <t xml:space="preserve">311239833</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSU bygningsrådgivning ApS</t>
+          <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-07-16</t>
+          <t xml:space="preserve">2027-04-07</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3116,40 +3116,40 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungsted Havn 34</t>
+          <t xml:space="preserve">Alsvej 83</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">717938, 7644227</t>
+          <t xml:space="preserve">2368570</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J42">
-        <v>303</v>
+        <v>393</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217548</t>
+          <t xml:space="preserve">311239833</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t xml:space="preserve">BF Byggeservice ApS</t>
+          <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-14</t>
+          <t xml:space="preserve">2027-04-07</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alsvej 83</t>
+          <t xml:space="preserve">Sdr. Jagtvej 10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2368570</t>
+          <t xml:space="preserve">2367182</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3210,11 +3210,11 @@
         </is>
       </c>
       <c r="J43">
-        <v>341</v>
+        <v>769</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239833</t>
+          <t xml:space="preserve">311259590</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-07</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3266,30 +3266,30 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alsvej 83</t>
+          <t xml:space="preserve">Stadionalle 11B</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2368570</t>
+          <t xml:space="preserve">9153682</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J44">
-        <v>393</v>
+        <v>4057</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239833</t>
+          <t xml:space="preserve">311259593</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-07</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sdr. Jagtvej 10</t>
+          <t xml:space="preserve">Usserød Kongevej 45</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367182</t>
+          <t xml:space="preserve">2367843</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3360,11 +3360,11 @@
         </is>
       </c>
       <c r="J45">
-        <v>769</v>
+        <v>458</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259590</t>
+          <t xml:space="preserve">311259586</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3416,30 +3416,30 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 11B</t>
+          <t xml:space="preserve">Ahornvej 50A</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">9153682</t>
+          <t xml:space="preserve">2367722</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J46">
-        <v>4057</v>
+        <v>368</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259593</t>
+          <t xml:space="preserve">311265087</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Usserød Kongevej 45</t>
+          <t xml:space="preserve">Ahornvej 50B</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3501,20 +3501,20 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367843</t>
+          <t xml:space="preserve">2367722</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J47">
-        <v>458</v>
+        <v>669</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259586</t>
+          <t xml:space="preserve">311265087</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahornvej 50A</t>
+          <t xml:space="preserve">Ahornvej 50C</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3581,11 +3581,11 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J48">
-        <v>368</v>
+        <v>500</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahornvej 50B</t>
+          <t xml:space="preserve">Lundevej 24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3651,20 +3651,20 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367722</t>
+          <t xml:space="preserve">9990363</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J49">
-        <v>669</v>
+        <v>112</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265087</t>
+          <t xml:space="preserve">311265098</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3716,30 +3716,30 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahornvej 50C</t>
+          <t xml:space="preserve">Stadionalle 11A</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367722</t>
+          <t xml:space="preserve">9153682</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J50">
-        <v>500</v>
+        <v>6610</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265087</t>
+          <t xml:space="preserve">311265094</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3791,30 +3791,30 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundevej 24</t>
+          <t xml:space="preserve">Stadionalle 5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990363</t>
+          <t xml:space="preserve">9153682</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J51">
-        <v>112</v>
+        <v>6457</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265098</t>
+          <t xml:space="preserve">311265099</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 11A</t>
+          <t xml:space="preserve">Stadionalle 5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3881,15 +3881,15 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J52">
-        <v>6610</v>
+        <v>176</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265094</t>
+          <t xml:space="preserve">311265099</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3956,15 +3956,15 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J53">
-        <v>6457</v>
+        <v>127</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265099</t>
+          <t xml:space="preserve">311265093</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4031,11 +4031,11 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J54">
-        <v>176</v>
+        <v>1595</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4091,30 +4091,30 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 5</t>
+          <t xml:space="preserve">Bloustrødvej 11A</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">9153682</t>
+          <t xml:space="preserve">2369496</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J55">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265093</t>
+          <t xml:space="preserve">311265958</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-09</t>
+          <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4166,30 +4166,30 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 5</t>
+          <t xml:space="preserve">Bloustrødvej 13B</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">9153682</t>
+          <t xml:space="preserve">7853948</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J56">
-        <v>1595</v>
+        <v>86</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265099</t>
+          <t xml:space="preserve">311336533</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-09</t>
+          <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 11A</t>
+          <t xml:space="preserve">Bloustrødvej 15A</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369496</t>
+          <t xml:space="preserve">2369498</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4260,11 +4260,11 @@
         </is>
       </c>
       <c r="J57">
-        <v>162</v>
+        <v>86</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265958</t>
+          <t xml:space="preserve">311265956</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 13B</t>
+          <t xml:space="preserve">Bloustrødvej 1A</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">7853948</t>
+          <t xml:space="preserve">9072790</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4335,11 +4335,11 @@
         </is>
       </c>
       <c r="J58">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311336533</t>
+          <t xml:space="preserve">311265960</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 15A</t>
+          <t xml:space="preserve">Bloustrødvej 1B</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369498</t>
+          <t xml:space="preserve">2369491</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4410,11 +4410,11 @@
         </is>
       </c>
       <c r="J59">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265956</t>
+          <t xml:space="preserve">311265961</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 1A</t>
+          <t xml:space="preserve">Bloustrødvej 21B</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9072790</t>
+          <t xml:space="preserve">2369539</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4485,11 +4485,11 @@
         </is>
       </c>
       <c r="J60">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265960</t>
+          <t xml:space="preserve">311265967</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 1B</t>
+          <t xml:space="preserve">Bloustrødvej 23A</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369491</t>
+          <t xml:space="preserve">7632534</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4560,11 +4560,11 @@
         </is>
       </c>
       <c r="J61">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265961</t>
+          <t xml:space="preserve">311265968</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 21B</t>
+          <t xml:space="preserve">Bloustrødvej 25B</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369539</t>
+          <t xml:space="preserve">8287549</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4635,11 +4635,11 @@
         </is>
       </c>
       <c r="J62">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265967</t>
+          <t xml:space="preserve">311265969</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 23A</t>
+          <t xml:space="preserve">Bloustrødvej 27A</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">7632534</t>
+          <t xml:space="preserve">2369536</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4710,11 +4710,11 @@
         </is>
       </c>
       <c r="J63">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265968</t>
+          <t xml:space="preserve">311265970</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 25B</t>
+          <t xml:space="preserve">Bloustrødvej 29A</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">8287549</t>
+          <t xml:space="preserve">7815341</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4785,11 +4785,11 @@
         </is>
       </c>
       <c r="J64">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265969</t>
+          <t xml:space="preserve">311265972</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 27A</t>
+          <t xml:space="preserve">Bloustrødvej 3B</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369536</t>
+          <t xml:space="preserve">7968240</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4860,11 +4860,11 @@
         </is>
       </c>
       <c r="J65">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265970</t>
+          <t xml:space="preserve">311265962</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 29A</t>
+          <t xml:space="preserve">Bloustrødvej 9A</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">7815341</t>
+          <t xml:space="preserve">7632535</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265972</t>
+          <t xml:space="preserve">311265966</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 3B</t>
+          <t xml:space="preserve">Selmersvej 13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">7968240</t>
+          <t xml:space="preserve">2366692</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5010,11 +5010,11 @@
         </is>
       </c>
       <c r="J67">
-        <v>96</v>
+        <v>613</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265962</t>
+          <t xml:space="preserve">311265957</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 9A</t>
+          <t xml:space="preserve">Stampevej 5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">7632535</t>
+          <t xml:space="preserve">2369502</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5085,11 +5085,11 @@
         </is>
       </c>
       <c r="J68">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265966</t>
+          <t xml:space="preserve">311265976</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selmersvej 13</t>
+          <t xml:space="preserve">Stampevej 7</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366692</t>
+          <t xml:space="preserve">2369501</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5160,11 +5160,11 @@
         </is>
       </c>
       <c r="J69">
-        <v>613</v>
+        <v>86</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265957</t>
+          <t xml:space="preserve">311337847</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Kommune</t>
+          <t xml:space="preserve">Anne-Mette Casparij</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stampevej 5</t>
+          <t xml:space="preserve">Selmersvej 1B</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369502</t>
+          <t xml:space="preserve">250251, 250252, 250253, 250261</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5235,21 +5235,21 @@
         </is>
       </c>
       <c r="J70">
-        <v>86</v>
+        <v>386</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265976</t>
+          <t xml:space="preserve">311269737</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danakon a/s</t>
+          <t xml:space="preserve">Boligeftersyn P/S</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-14</t>
+          <t xml:space="preserve">2027-08-30</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stampevej 7</t>
+          <t xml:space="preserve">Rungstedvej 31</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5301,20 +5301,20 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369501</t>
+          <t xml:space="preserve">8101069</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J71">
-        <v>86</v>
+        <v>267</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311337847</t>
+          <t xml:space="preserve">311269866</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-14</t>
+          <t xml:space="preserve">2027-08-31</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anne-Mette Casparij</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selmersvej 1B</t>
+          <t xml:space="preserve">Sdr. Jagtvej 10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5376,30 +5376,30 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">250251, 250252, 250253, 250261</t>
+          <t xml:space="preserve">2367182</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J72">
-        <v>386</v>
+        <v>203</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269737</t>
+          <t xml:space="preserve">311269865</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boligeftersyn P/S</t>
+          <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-30</t>
+          <t xml:space="preserve">2027-08-31</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,30 +5441,30 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungstedvej 31</t>
+          <t xml:space="preserve">Stadionalle 4</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">8101069</t>
+          <t xml:space="preserve">2381983</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J73">
-        <v>267</v>
+        <v>521</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269866</t>
+          <t xml:space="preserve">311270049</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sdr. Jagtvej 10</t>
+          <t xml:space="preserve">Bibliotekstorvet 1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5526,20 +5526,20 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367182</t>
+          <t xml:space="preserve">246772</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J74">
-        <v>203</v>
+        <v>5875</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269865</t>
+          <t xml:space="preserve">311272829</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-31</t>
+          <t xml:space="preserve">2027-09-14</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 4</t>
+          <t xml:space="preserve">Kokkedal Stationsvej 3</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381983</t>
+          <t xml:space="preserve">2369157</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5610,11 +5610,11 @@
         </is>
       </c>
       <c r="J75">
-        <v>521</v>
+        <v>476</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270049</t>
+          <t xml:space="preserve">311272832</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-31</t>
+          <t xml:space="preserve">2027-09-14</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bibliotekstorvet 1</t>
+          <t xml:space="preserve">Lundevej 18</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">246772</t>
+          <t xml:space="preserve">9990363</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5685,11 +5685,11 @@
         </is>
       </c>
       <c r="J76">
-        <v>5875</v>
+        <v>88</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272829</t>
+          <t xml:space="preserve">311272831</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kokkedal Stationsvej 3</t>
+          <t xml:space="preserve">Lundevej 20</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5751,20 +5751,20 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369157</t>
+          <t xml:space="preserve">9990363</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J77">
-        <v>476</v>
+        <v>88</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272832</t>
+          <t xml:space="preserve">311272831</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundevej 18</t>
+          <t xml:space="preserve">Breeltevej 3</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990363</t>
+          <t xml:space="preserve">100019618</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5835,11 +5835,11 @@
         </is>
       </c>
       <c r="J78">
-        <v>88</v>
+        <v>1306</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272831</t>
+          <t xml:space="preserve">311279819</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-14</t>
+          <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundevej 20</t>
+          <t xml:space="preserve">Gasværksvej 1</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5901,20 +5901,20 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990363</t>
+          <t xml:space="preserve">2367211</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J79">
-        <v>88</v>
+        <v>430</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272831</t>
+          <t xml:space="preserve">311279821</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-14</t>
+          <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breeltevej 3</t>
+          <t xml:space="preserve">Kokkedal Alle 1</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">100019618</t>
+          <t xml:space="preserve">9761663</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5985,11 +5985,11 @@
         </is>
       </c>
       <c r="J80">
-        <v>1306</v>
+        <v>169</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279819</t>
+          <t xml:space="preserve">311279820</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasværksvej 1</t>
+          <t xml:space="preserve">Skovvænget 36</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367211</t>
+          <t xml:space="preserve">2366957</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6060,11 +6060,11 @@
         </is>
       </c>
       <c r="J81">
-        <v>430</v>
+        <v>744</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279821</t>
+          <t xml:space="preserve">311286269</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-23</t>
+          <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kokkedal Alle 1</t>
+          <t xml:space="preserve">Sophielund 25</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">9761663</t>
+          <t xml:space="preserve">2369150</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6135,11 +6135,11 @@
         </is>
       </c>
       <c r="J82">
-        <v>169</v>
+        <v>1941</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279820</t>
+          <t xml:space="preserve">311286265</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-23</t>
+          <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvænget 36</t>
+          <t xml:space="preserve">Rungstedvej 1</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366957</t>
+          <t xml:space="preserve">2367324</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6210,11 +6210,11 @@
         </is>
       </c>
       <c r="J83">
-        <v>744</v>
+        <v>2151</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286269</t>
+          <t xml:space="preserve">311288806</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-29</t>
+          <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sophielund 25</t>
+          <t xml:space="preserve">Ådalsvej 52</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369150</t>
+          <t xml:space="preserve">2369817</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -6285,11 +6285,11 @@
         </is>
       </c>
       <c r="J84">
-        <v>1941</v>
+        <v>1351</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286265</t>
+          <t xml:space="preserve">311288805</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-29</t>
+          <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6341,17 +6341,17 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 10</t>
+          <t xml:space="preserve">Ådalsvej 52</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381978</t>
+          <t xml:space="preserve">2369817</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6360,11 +6360,11 @@
         </is>
       </c>
       <c r="J85">
-        <v>186</v>
+        <v>1171</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286266</t>
+          <t xml:space="preserve">311288805</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-29</t>
+          <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6416,22 +6416,22 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 8</t>
+          <t xml:space="preserve">Ved Møllen 10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381978</t>
+          <t xml:space="preserve">2367436</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J86">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286267</t>
+          <t xml:space="preserve">311289218</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-29</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungstedvej 1</t>
+          <t xml:space="preserve">Ved Møllen 10</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6501,20 +6501,20 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367324</t>
+          <t xml:space="preserve">2367436</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J87">
-        <v>2151</v>
+        <v>166</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288806</t>
+          <t xml:space="preserve">311289219</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-14</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsvej 52</t>
+          <t xml:space="preserve">Selmersvej 6</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6576,20 +6576,20 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369817</t>
+          <t xml:space="preserve">8101069</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J88">
-        <v>1351</v>
+        <v>1691</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288805</t>
+          <t xml:space="preserve">311289939</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-14</t>
+          <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsvej 52</t>
+          <t xml:space="preserve">Selmersvej 6</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6651,20 +6651,20 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369817</t>
+          <t xml:space="preserve">8101069</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J89">
-        <v>1171</v>
+        <v>3265</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288805</t>
+          <t xml:space="preserve">311289940</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-14</t>
+          <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Møllen 10</t>
+          <t xml:space="preserve">Selmersvej 6</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6726,20 +6726,20 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367436</t>
+          <t xml:space="preserve">8101069</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J90">
-        <v>140</v>
+        <v>1610</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289218</t>
+          <t xml:space="preserve">311289942</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Møllen 10</t>
+          <t xml:space="preserve">Selmersvej 6</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6801,20 +6801,20 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367436</t>
+          <t xml:space="preserve">8101069</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J91">
-        <v>166</v>
+        <v>2388</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289219</t>
+          <t xml:space="preserve">311289943</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6881,15 +6881,15 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J92">
-        <v>1691</v>
+        <v>474</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289939</t>
+          <t xml:space="preserve">311289945</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selmersvej 6</t>
+          <t xml:space="preserve">Stampevej 10</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6951,20 +6951,20 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8101069</t>
+          <t xml:space="preserve">2370057</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J93">
-        <v>3265</v>
+        <v>240</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289940</t>
+          <t xml:space="preserve">311291492</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-21</t>
+          <t xml:space="preserve">2028-01-08</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selmersvej 6</t>
+          <t xml:space="preserve">Ådalsparkvej 2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7026,20 +7026,20 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">8101069</t>
+          <t xml:space="preserve">2369282</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J94">
-        <v>1610</v>
+        <v>8807</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289942</t>
+          <t xml:space="preserve">311298940</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-21</t>
+          <t xml:space="preserve">2028-02-21</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selmersvej 6</t>
+          <t xml:space="preserve">Ådalsparkvej 2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7101,20 +7101,20 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">8101069</t>
+          <t xml:space="preserve">2369282</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J95">
-        <v>2388</v>
+        <v>2450</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289943</t>
+          <t xml:space="preserve">311298940</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-21</t>
+          <t xml:space="preserve">2028-02-21</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selmersvej 6</t>
+          <t xml:space="preserve">Ådalsparkvej 2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7176,20 +7176,20 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">8101069</t>
+          <t xml:space="preserve">2369282</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J96">
-        <v>474</v>
+        <v>1637</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289945</t>
+          <t xml:space="preserve">311298938</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-21</t>
+          <t xml:space="preserve">2028-02-21</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7241,30 +7241,30 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stampevej 10</t>
+          <t xml:space="preserve">Østre Stationsvej 1A</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2370057</t>
+          <t xml:space="preserve">2380704</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J97">
-        <v>240</v>
+        <v>154</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291492</t>
+          <t xml:space="preserve">311306142</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-08</t>
+          <t xml:space="preserve">2028-04-03</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7316,30 +7316,30 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 2</t>
+          <t xml:space="preserve">Østre Stationsvej 1A</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369282</t>
+          <t xml:space="preserve">2380704</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J98">
-        <v>8807</v>
+        <v>95</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298940</t>
+          <t xml:space="preserve">311306140</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-21</t>
+          <t xml:space="preserve">2028-04-03</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7391,30 +7391,30 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 2</t>
+          <t xml:space="preserve">Østre Stationsvej 1A</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369282</t>
+          <t xml:space="preserve">2380704</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J99">
-        <v>2450</v>
+        <v>1507</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298940</t>
+          <t xml:space="preserve">311306137</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-21</t>
+          <t xml:space="preserve">2028-04-03</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7466,30 +7466,30 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 2</t>
+          <t xml:space="preserve">Østre Stationsvej 1A</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369282</t>
+          <t xml:space="preserve">2380704</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J100">
-        <v>1637</v>
+        <v>2099</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298938</t>
+          <t xml:space="preserve">311308266</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-21</t>
+          <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 12</t>
+          <t xml:space="preserve">Østre Stationsvej 1A</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7551,20 +7551,20 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381978</t>
+          <t xml:space="preserve">2380704</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J101">
-        <v>6712</v>
+        <v>3262</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311304707</t>
+          <t xml:space="preserve">311308262</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-23</t>
+          <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7631,15 +7631,15 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J102">
-        <v>154</v>
+        <v>614</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306142</t>
+          <t xml:space="preserve">311308267</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-03</t>
+          <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7691,40 +7691,40 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Stationsvej 1A</t>
+          <t xml:space="preserve">Ådalsparkvej 4N</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2380704</t>
+          <t xml:space="preserve">2369282</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J103">
-        <v>95</v>
+        <v>408</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306140</t>
+          <t xml:space="preserve">311420783</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danakon a/s</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-03</t>
+          <t xml:space="preserve">2030-02-04</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Kommune</t>
+          <t xml:space="preserve">Hørsholm Almene Boligselskab</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -7766,40 +7766,40 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Stationsvej 1A</t>
+          <t xml:space="preserve">Sophielund 88</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2380704</t>
+          <t xml:space="preserve">247821, 247822</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J104">
-        <v>1507</v>
+        <v>3028</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306137</t>
+          <t xml:space="preserve">311623696</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danakon a/s</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-03</t>
+          <t xml:space="preserve">2032-08-29</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Kommune</t>
+          <t xml:space="preserve">Hørsholm Almene Boligselskab</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7841,40 +7841,40 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Stationsvej 1A</t>
+          <t xml:space="preserve">Louiselund 2</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2380704</t>
+          <t xml:space="preserve">413034, 413035</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J105">
-        <v>2099</v>
+        <v>7932</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308266</t>
+          <t xml:space="preserve">311626143</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danakon a/s</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-13</t>
+          <t xml:space="preserve">2032-09-07</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Kommune</t>
+          <t xml:space="preserve">Hørsholm Almene Boligselskab</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7916,40 +7916,40 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Stationsvej 1A</t>
+          <t xml:space="preserve">Louiselund 7</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2380704</t>
+          <t xml:space="preserve">413034, 413035</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J106">
-        <v>3262</v>
+        <v>4467</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308262</t>
+          <t xml:space="preserve">311626082</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danakon a/s</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-13</t>
+          <t xml:space="preserve">2032-09-07</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7976,12 +7976,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Kommune</t>
+          <t xml:space="preserve">Hørsholm Almene Boligselskab</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7991,40 +7991,40 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Stationsvej 1A</t>
+          <t xml:space="preserve">Kong Georgsvej 9</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2950</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2380704</t>
+          <t xml:space="preserve">246868, 246869</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J107">
-        <v>614</v>
+        <v>2508</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308267</t>
+          <t xml:space="preserve">311626489</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danakon a/s</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-13</t>
+          <t xml:space="preserve">2032-09-08</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Kommune</t>
+          <t xml:space="preserve">Jianting Du</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 4N</t>
+          <t xml:space="preserve">Moldrupvej 13</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8076,30 +8076,30 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369282</t>
+          <t xml:space="preserve">100893889, 100893890</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J108">
-        <v>408</v>
+        <v>193</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420783</t>
+          <t xml:space="preserve">311809573</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-04</t>
+          <t xml:space="preserve">2035-02-04</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Almene Boligselskab</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sophielund 88</t>
+          <t xml:space="preserve">Rungstedvej 23</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">247821, 247822</t>
+          <t xml:space="preserve">2366696</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8160,21 +8160,21 @@
         </is>
       </c>
       <c r="J109">
-        <v>3028</v>
+        <v>445</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623696</t>
+          <t xml:space="preserve">311892520</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-29</t>
+          <t xml:space="preserve">2036-04-08</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8201,12 +8201,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Almene Boligselskab</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Louiselund 2</t>
+          <t xml:space="preserve">Hørsholm Alle 4</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,30 +8226,30 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">413034, 413035</t>
+          <t xml:space="preserve">2367940</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J110">
-        <v>7932</v>
+        <v>350</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626143</t>
+          <t xml:space="preserve">311893229</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-07</t>
+          <t xml:space="preserve">2036-04-10</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Almene Boligselskab</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Louiselund 7</t>
+          <t xml:space="preserve">Hørsholm Alle 4</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8301,30 +8301,30 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">413034, 413035</t>
+          <t xml:space="preserve">2367940</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J111">
-        <v>4467</v>
+        <v>2855</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626082</t>
+          <t xml:space="preserve">311893225</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-07</t>
+          <t xml:space="preserve">2036-04-10</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Almene Boligselskab</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8366,17 +8366,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Georgsvej 9</t>
+          <t xml:space="preserve">Mariehøj Alle 1</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2950</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">246868, 246869</t>
+          <t xml:space="preserve">7951098</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -8385,21 +8385,21 @@
         </is>
       </c>
       <c r="J112">
-        <v>2508</v>
+        <v>690</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626489</t>
+          <t xml:space="preserve">311912380</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-08</t>
+          <t xml:space="preserve">2036-07-02</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jianting Du</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moldrupvej 13</t>
+          <t xml:space="preserve">Lundevej 26</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">100893889, 100893890</t>
+          <t xml:space="preserve">9153647</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8460,21 +8460,21 @@
         </is>
       </c>
       <c r="J113">
-        <v>193</v>
+        <v>840</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809573</t>
+          <t xml:space="preserve">311915684</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-04</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungstedvej 23</t>
+          <t xml:space="preserve">Gl Byvej 10</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366696</t>
+          <t xml:space="preserve">7966206</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8535,11 +8535,11 @@
         </is>
       </c>
       <c r="J114">
-        <v>445</v>
+        <v>1343</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892520</t>
+          <t xml:space="preserve">311916600</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-08</t>
+          <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Alle 4</t>
+          <t xml:space="preserve">Gl Byvej 10</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8601,20 +8601,20 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367940</t>
+          <t xml:space="preserve">7966206</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J115">
-        <v>350</v>
+        <v>929</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893229</t>
+          <t xml:space="preserve">311916600</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-10</t>
+          <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Alle 4</t>
+          <t xml:space="preserve">Gl Byvej 10</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367940</t>
+          <t xml:space="preserve">7966206</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8685,11 +8685,11 @@
         </is>
       </c>
       <c r="J116">
-        <v>2855</v>
+        <v>2007</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893225</t>
+          <t xml:space="preserve">311916600</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-10</t>
+          <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mariehøj Alle 1</t>
+          <t xml:space="preserve">Gl Byvej 10</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,20 +8751,20 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">7951098</t>
+          <t xml:space="preserve">7966206</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J117">
-        <v>690</v>
+        <v>599</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912380</t>
+          <t xml:space="preserve">311916600</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-02</t>
+          <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundevej 26</t>
+          <t xml:space="preserve">Gl Byvej 10</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8826,20 +8826,20 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">9153647</t>
+          <t xml:space="preserve">7966206</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J118">
-        <v>840</v>
+        <v>3389</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915684</t>
+          <t xml:space="preserve">311916600</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8906,11 +8906,11 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J119">
-        <v>1343</v>
+        <v>156</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Byvej 10</t>
+          <t xml:space="preserve">Lundevej 19</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8981,11 +8981,11 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J120">
-        <v>929</v>
+        <v>2456</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Byvej 10</t>
+          <t xml:space="preserve">Sdr. Jagtvej 2</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9051,20 +9051,20 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">7966206</t>
+          <t xml:space="preserve">2367273</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J121">
-        <v>2007</v>
+        <v>163</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916600</t>
+          <t xml:space="preserve">311923296</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-30</t>
+          <t xml:space="preserve">2036-09-02</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,30 +9116,30 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Byvej 10</t>
+          <t xml:space="preserve">Stadionalle 10</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">7966206</t>
+          <t xml:space="preserve">2381978</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J122">
-        <v>599</v>
+        <v>186</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916600</t>
+          <t xml:space="preserve">311931619</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-30</t>
+          <t xml:space="preserve">2036-10-13</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,30 +9191,30 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Byvej 10</t>
+          <t xml:space="preserve">Stadionalle 12</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">7966206</t>
+          <t xml:space="preserve">2381978</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J123">
-        <v>3389</v>
+        <v>6712</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916600</t>
+          <t xml:space="preserve">311931619</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-30</t>
+          <t xml:space="preserve">2036-10-13</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,30 +9266,30 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Byvej 10</t>
+          <t xml:space="preserve">Stadionalle 8</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">7966206</t>
+          <t xml:space="preserve">2381978</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J124">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916600</t>
+          <t xml:space="preserve">311931619</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-30</t>
+          <t xml:space="preserve">2036-10-13</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,30 +9341,30 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundevej 19</t>
+          <t xml:space="preserve">Stadionalle 8</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">7966206</t>
+          <t xml:space="preserve">2381978</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J125">
-        <v>2456</v>
+        <v>2800</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916600</t>
+          <t xml:space="preserve">311931619</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-30</t>
+          <t xml:space="preserve">2036-10-13</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,30 +9416,30 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sdr. Jagtvej 2</t>
+          <t xml:space="preserve">Stadionalle 8</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367273</t>
+          <t xml:space="preserve">2381978</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J126">
-        <v>163</v>
+        <v>200</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923296</t>
+          <t xml:space="preserve">311931619</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-02</t>
+          <t xml:space="preserve">2036-10-13</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
